--- a/GeoMIP/results/validacion_jerarquico.xlsx
+++ b/GeoMIP/results/validacion_jerarquico.xlsx
@@ -526,10 +526,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0382</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>0.005</v>
+        <v>0.0113</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -572,10 +572,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0546</v>
+        <v>0.1031</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0075</v>
+        <v>0.0167</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
@@ -618,10 +618,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0083</v>
+        <v>0.0168</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0028</v>
+        <v>0.0054</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -664,10 +664,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0234</v>
+        <v>0.021</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007</v>
+        <v>0.0091</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -710,10 +710,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0145</v>
+        <v>0.0225</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0044</v>
+        <v>0.0089</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -756,10 +756,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0152</v>
+        <v>0.0328</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0066</v>
+        <v>0.0112</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -802,10 +802,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0401</v>
+        <v>0.0655</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0063</v>
+        <v>0.0081</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -848,10 +848,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0544</v>
+        <v>0.1018</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0077</v>
+        <v>0.0142</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -894,10 +894,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4496</v>
+        <v>0.952</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0097</v>
+        <v>0.0224</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -940,10 +940,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>2.3565</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0157</v>
+        <v>0.0306</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -986,10 +986,10 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1199</v>
+        <v>0.2381</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0076</v>
+        <v>0.0126</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -1032,10 +1032,10 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2258</v>
+        <v>0.5413</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0113</v>
+        <v>0.0194</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -1078,10 +1078,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0277</v>
+        <v>0.0573</v>
       </c>
       <c r="J14" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
@@ -1124,10 +1124,10 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0421</v>
+        <v>0.0862</v>
       </c>
       <c r="J15" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0139</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -1170,10 +1170,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4525</v>
+        <v>0.9021</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0098</v>
+        <v>0.0169</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1216,10 +1216,10 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1074</v>
+        <v>2.4967</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0165</v>
+        <v>0.0356</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1255,7 +1255,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>4.77</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
